--- a/data_extactor/batch_10_fa/trimmed/batch_0097_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0097_fa_trim.xlsx
@@ -503,22 +503,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Electronic train management systems ETMS | نرم‌افزار نقشه‌برداری مسیر | Microsoft Excel | Microsoft Word | نرم‌افزار ثبت و ردیابی زمان</t>
+          <t>Electronic train management systems ETMS | نرم‌افزار نقشه‌برداری مسیر | Microsoft Excel | نرم‌افزار ثبت و ردیابی زمان</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و تدریس | خدمات مشتریان و خدمات فردی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | زبان انگلیسی | آموزش و پرورش | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید دور | توجه انتخابی | دقت کنترل | دید نزدیک | ادراک عمق | حساسیت به مسئله | زمان واکنش</t>
+          <t>بینایی دور | توجه انتخابی | دقت کنترل | بینایی نزدیک | درک عمق | حساسیت به مسئله | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متصدیان اعزام و دیسپچری به‌استثنای پلیس، آتش‌نشانی و اورژانس | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | تعمیرکاران سیستم‌های علائم و سوزن‌های خطوط راه‌آهن | رانندگان مترو و تراموا | بازرسان حمل‌ونقل</t>
+          <t>متصدیان دیسپاچ و اعزام | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن | رانندگان مترو و تراموا | بازرسان ترابری و حمل‌ونقل</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | مدیریت و امور اداری | مکانیک | زبان انگلیسی | خدمات مشتریان و خدمات فردی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مدیریت و اداره | مکانیک | زبان انگلیسی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | دید دور | دقت کنترل | زمان واکنش | دید نزدیک | توجه انتخابی</t>
+          <t>درک شفاهی | حساسیت به مسئله | بینایی دور | دقت کنترل | زمان عکس‌العمل | بینایی نزدیک | توجه انتخابی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتورهای جرثقیل و تاورکرین | متصدیان اعزام و دیسپچری به‌استثنای پلیس، آتش‌نشانی و اورژانس | اپراتورهای تراکتور و لیفتراک‌های صنعتی | لکوموتیورانان | تعمیرکاران واگن‌های ریلی | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن</t>
+          <t>اپراتورهای جرثقیل و تاورکرین | متصدیان دیسپاچ و اعزام | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | لکوموتیورانان | تعمیرکار واگن قطار | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دقت کنترل | دید نزدیک | ثبات دست و بازو | دید دور | درک شفاهی | زمان واکنش | حساسیت به مسئله</t>
+          <t>دقت کنترل | بینایی نزدیک | ثبات دست و بازو | بینایی دور | درک شفاهی | زمان عکس‌العمل | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>اپراتورهای جرثقیل و تاورکرین | اپراتورهای بالابر و وینچ | لکوموتیورانان | تعمیرکاران واگن‌های ریلی | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | رؤسای قطار و مدیران محوطه راه‌آهن | تعمیرکاران سیستم‌های علائم و سوزن‌های خطوط راه‌آهن</t>
+          <t>اپراتورهای جرثقیل و تاورکرین | اپراتورهای بالابر و وینچ | لکوموتیورانان | تعمیرکار واگن قطار | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | رؤسای قطار و مدیران محوطه راه‌آهن | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | یادگیری فعال | نگارش</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حمل‌ونقل | زبان انگلیسی | آموزش و تدریس | امور حقوقی و دولتی</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | زبان انگلیسی | آموزش و پرورش | قانون و دولت</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | دید دور | دید نزدیک | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | بینایی دور | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>متصدیان اعزام و دیسپچری به‌استثنای پلیس، آتش‌نشانی و اورژانس | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل جابه‌جایی بار | لکوموتیورانان | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رانندگان مترو و تراموا | بازرسان حمل‌ونقل</t>
+          <t>متصدیان دیسپاچ و اعزام | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | لکوموتیورانان | لکوموتیورانان محوطه راه‌آهن و رانندگان لکوموتیوهای کوچک مانوری | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رانندگان مترو و تراموا | بازرسان ترابری و حمل‌ونقل</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | نظارت | درک مطلب | یادگیری فعال | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | نظارت | درک مطلب | یادگیری فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>دقت کنترل | هماهنگی چنداندامی | زمان واکنش | کنترل نرخ حرکتی | دید نزدیک | دید دور | توجه انتخابی</t>
+          <t>دقت کنترل | هماهنگی چند عضو | زمان عکس‌العمل | کنترل نرخ | بینایی نزدیک | بینایی دور | توجه انتخابی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | متصدیان اعزام و دیسپچری به‌استثنای پلیس، آتش‌نشانی و اورژانس | لکوموتیورانان | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | رانندگان تاکسی | پلیس راه‌آهن و ناوگان حمل‌ونقل عمومی</t>
+          <t>رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | متصدیان دیسپاچ و اعزام | لکوموتیورانان | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رؤسای قطار و مدیران محوطه راه‌آهن | رانندگان تاکسی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | مخابرات | جغرافیا | ریاضیات</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | مخابرات | جغرافیا | ریاضیات</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی چنداندامی | دقت کنترل | قدرت ایستا | دید نزدیک</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>لکوموتیورانان | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رانندگان مترو و تراموا | تعمیرکاران واگن‌های ریلی | اپراتورهای ماشین‌آلات ریل‌گذاری و نگهداری خطوط راه‌آهن | متصدیان اعزام و دیسپچری به‌استثنای پلیس، آتش‌نشانی و اورژانس</t>
+          <t>لکوموتیورانان | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان ترمز، علائم و سوزن‌بانی راه‌آهن و آتشکاران لکوموتیو | رانندگان مترو و تراموا | تعمیرکار واگن قطار | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | متصدیان دیسپاچ و اعزام</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حمل‌ونقل | مکانیک</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | مکانیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید دور | دقت کنترل | درک شفاهی | حساسیت به مسئله | ادراک عمق | ثبات دست و بازو | هماهنگی چنداندامی</t>
+          <t>بینایی دور | دقت کنترل | درک شفاهی | حساسیت به مسئله | درک عمق | ثبات دست و بازو | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | غواصان تجاری و صنعتی | کارگران صید و شکار | مکانیک‌ها و تعمیرکاران قایق‌های موتوری | قایقرانان قایق‌های موتوری | ریگرها و متصدیان دکل‌بندی و مهار بار | مهندسان فنی کشتی</t>
+          <t>کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | غواصان تجاری و صنعتی | صیادان، ماهیگیران و شکارچیان | مکانیک و تکنسین شناورهای موتوری | قایقرانان قایق‌های موتوری | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | مهندسان فنی کشتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>سخن گفتن | نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>حمل‌ونقل | ایمنی و امنیت عمومی | مکانیک | امور حقوقی و دولتی | زبان انگلیسی | جغرافیا | مدیریت و امور اداری</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | قانون و دولت | زبان انگلیسی | جغرافیا | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | جهت‌یابی فضایی | دید دور | دقت کنترل</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | جهت‌گیری فضایی | بینایی دور | دقت کنترل</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>متصدیان پل‌های متحرک و آب‌بندها | مهندسان کشتی‌سازی و معماری دریایی | قایقرانان قایق‌های موتوری | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان فنی کشتی | متصدیان بارگیری مخزن‌دار ریلی، کامیونی و کشتی | بازرسان حمل‌ونقل</t>
+          <t>متصدیان پل‌های متحرک و حوضچه‌های آرامش | مهندسان دریایی و معماران کشتی | قایقرانان قایق‌های موتوری | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان فنی کشتی | متصدیان بارگیری مخزن‌دار ریلی، تانکر جاده‌ای و کشتی | بازرسان ترابری و حمل‌ونقل</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | شنیدن فعال | تفکر انتقادی</t>
+          <t>سخن گفتن | نظارت | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | آموزش و تدریس | ایمنی و امنیت عمومی | حمل‌ونقل | مکانیک</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | آموزش و پرورش | ایمنی و امنیت عمومی | حمل و نقل | مکانیک</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دقت کنترل | جهت‌یابی فضایی | دید دور | حساسیت به مسئله | ثبات دست و بازو | چابکی دستی | ادراک عمق</t>
+          <t>دقت کنترل | جهت‌گیری فضایی | بینایی دور | حساسیت به مسئله | ثبات دست و بازو | مهارت دستی | درک عمق</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متصدیان پل‌های متحرک و آب‌بندها | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | اپراتورهای لایروب | کارگران صید و شکار | مکانیک‌ها و تعمیرکاران قایق‌های موتوری | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان فنی کشتی</t>
+          <t>متصدیان پل‌های متحرک و حوضچه‌های آرامش | کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | اپراتورهای لایروب | صیادان، ماهیگیران و شکارچیان | مکانیک و تکنسین شناورهای موتوری | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان فنی کشتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | نظارت | سخن گفتن | یادگیری فعال | درک مطلب | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | نظارت | سخن گفتن | یادگیری فعال | درک مطلب | نگارش</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | فنی و مهندسی | ایمنی و امنیت عمومی | حمل‌ونقل | ریاضیات | رایانه و الکترونیک</t>
+          <t>مکانیک | زبان انگلیسی | مهندسی و فناوری | ایمنی و امنیت عمومی | حمل و نقل | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | درک کتبی | دقت کنترل | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | دقت کنترل | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مهندسان کشتی‌سازی و معماری دریایی | مکانیک‌ها و تعمیرکاران قایق‌های موتوری | اپراتورهای نیروگاه برق | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان تأسیسات و اپراتورهای دیگ بخار</t>
+          <t>مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مهندسان دریایی و معماران کشتی | مکانیک و تکنسین شناورهای موتوری | اپراتورهای نیروگاه برق | ملوانان و روغن‌کاران شناورهای دریایی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
